--- a/portal-web/data/source-conferencistas/Participacion jornadas.xlsx
+++ b/portal-web/data/source-conferencistas/Participacion jornadas.xlsx
@@ -1702,9 +1702,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3B845049-F7AD-49C2-9B60-1D64B5A6D719}" name="tblParticipantesWeb" displayName="tblParticipantesWeb" ref="A1:AB13" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
-  <autoFilter ref="A1:AB13" xr:uid="{3B845049-F7AD-49C2-9B60-1D64B5A6D719}"/>
-  <tableColumns count="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3B845049-F7AD-49C2-9B60-1D64B5A6D719}" name="tblParticipantesWeb" displayName="tblParticipantesWeb" ref="A1:AE13" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+  <autoFilter ref="A1:AE13" xr:uid="{3B845049-F7AD-49C2-9B60-1D64B5A6D719}"/>
+  <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{8F8C6840-79E6-4189-B5B0-93B41F28D108}" name="id_registro" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{2F7D01C2-8836-4ED3-BE58-70A8E4DA99D6}" name="id_jornada" dataDxfId="28"/>
     <tableColumn id="3" xr3:uid="{B768C9DF-286B-40BA-A793-B5EA5B84F756}" name="jornada" dataDxfId="22"/>
@@ -1733,6 +1733,9 @@
     <tableColumn id="26" xr3:uid="{CA9921E3-7A4D-4450-939F-5BE3735AC9CD}" name="orden_card" dataDxfId="27"/>
     <tableColumn id="27" xr3:uid="{4A23AD6E-7472-4DF3-B60A-30E179BA21B9}" name="tipo_card" dataDxfId="26"/>
     <tableColumn id="28" xr3:uid="{23825030-4431-44B5-AF5D-B3D5A4129CD3}" name="publicar" dataDxfId="25"/>
+    <tableColumn id="29" xr3:uid="{A1B2C3D4-0001-4E00-8000-000000000001}" name="titulo_profesional"/>
+    <tableColumn id="30" xr3:uid="{A1B2C3D4-0001-4E00-8000-000000000002}" name="formacion_academica"/>
+    <tableColumn id="31" xr3:uid="{A1B2C3D4-0001-4E00-8000-000000000003}" name="trayectoria_destacada"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2471,7 +2474,7 @@
   <sheetPr>
     <tabColor rgb="FF4472C4"/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
@@ -2502,9 +2505,12 @@
     <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="34" customWidth="1"/>
+    <col min="30" max="30" width="55" customWidth="1"/>
+    <col min="31" max="31" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="64" t="s">
         <v>58</v>
       </c>
@@ -2589,8 +2595,23 @@
       <c r="AB1" s="65" t="s">
         <v>155</v>
       </c>
+      <c r="AC1" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">titulo_profesional</t>
+        </is>
+      </c>
+      <c r="AD1" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formacion_academica</t>
+        </is>
+      </c>
+      <c r="AE1" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trayectoria_destacada</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="64">
         <v>1</v>
       </c>
@@ -2663,8 +2684,11 @@
       <c r="AB2" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC2" s="69"/>
+      <c r="AD2" s="69"/>
+      <c r="AE2" s="69"/>
     </row>
-    <row r="3" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="64">
         <v>2</v>
       </c>
@@ -2737,8 +2761,11 @@
       <c r="AB3" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC3" s="69"/>
+      <c r="AD3" s="69"/>
+      <c r="AE3" s="69"/>
     </row>
-    <row r="4" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="64">
         <v>3</v>
       </c>
@@ -2817,8 +2844,28 @@
       <c r="AB4" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC4" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exrectora de la Universidad Colegio Mayor de Cundinamarca</t>
+        </is>
+      </c>
+      <c r="AD4" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Doctora en Administración (México)
+MBA
+Magíster en Docencia Universitaria</t>
+        </is>
+      </c>
+      <c r="AE4" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exrectora de la Universidad Colegio Mayor de Cundinamarca y actual miembro del Consejo Superior Universitario
+Más de 27 años de experiencia en educación superior, liderazgo estratégico y gestión del talento humano
+Experta en diseño curricular, autoevaluación, acreditación de alta calidad y virtualización académica (COIL y clases espejo)
+Investigadora Junior (Colciencias 2024), vinculada a grupos A1 y con trayectoria como conferencista y consultora</t>
+        </is>
+      </c>
     </row>
-    <row r="5" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="64">
         <v>4</v>
       </c>
@@ -2897,8 +2944,28 @@
       <c r="AB5" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC5" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente permanente, Universidade Federal do Delta do Parnaíba (Brasil)</t>
+        </is>
+      </c>
+      <c r="AD5" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Doctora en Psicología de la Educación, Universidad de Barcelona
+Máster en Psicología de la Educación y Psicología Social
+Licenciada en Psicología</t>
+        </is>
+      </c>
+      <c r="AE5" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ex Vicerrectora Académica, investigadora y líder de proyectos en educación superior, innovación educativa y tecnologías digitales aplicadas al aprendizaje
+Más de 20 años de experiencia en docencia, gestión académica e investigación en psicología y educación
+Liderazgo académico, producción científica y coordinación de grupos de investigación con reconocimiento nacional e internacional
+Reconocimientos: Premio Mujer Destacada 2024 y Doctor Honoris Causa 2023</t>
+        </is>
+      </c>
     </row>
-    <row r="6" spans="1:28" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="64">
         <v>5</v>
       </c>
@@ -2981,8 +3048,27 @@
       <c r="AB6" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC6" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viceministro de Educación Superior de Colombia</t>
+        </is>
+      </c>
+      <c r="AD6" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licenciado en Ciencias Sociales
+Magíster en Investigación Social Interdisciplinaria, Universidad Distrital
+Estudios de maestría en Estudios Políticos, Universidad Nacional de Colombia</t>
+        </is>
+      </c>
+      <c r="AE6" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se ha destacado por ocupar cargos de liderazgo en el sector educativo nacional y distrital
+Lideró proyectos estratégicos para fortalecer el acceso y la cobertura de la educación superior
+Consultor del PNUD y participante en la formulación de políticas de educación y paz en Colombia</t>
+        </is>
+      </c>
     </row>
-    <row r="7" spans="1:28" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="64">
         <v>6</v>
       </c>
@@ -3065,8 +3151,11 @@
       <c r="AB7" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC7" s="69"/>
+      <c r="AD7" s="69"/>
+      <c r="AE7" s="69"/>
     </row>
-    <row r="8" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="64">
         <v>7</v>
       </c>
@@ -3147,8 +3236,27 @@
       <c r="AB8" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC8" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Director Colombia, IXL Center</t>
+        </is>
+      </c>
+      <c r="AD8" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBA, Hult International Business School
+No Code AI and Machine Learning: Building Data Science Solutions, MIT Professional Education</t>
+        </is>
+      </c>
+      <c r="AE8" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Responsable de la implementación de sistemas de innovación en más de 800 empresas alrededor del mundo, con crecimiento y opciones estratégicas en Colombia, Guatemala, Honduras, México y España
+En el Innovation Management Institute ha impartido cursos de formación y certificación en innovación a más de 2.000 personas en todo el mundo
+Entrenador, mentor y facilitador de más de 300 equipos a nivel global
+Capacitó y educó a más de 2.000 personas en sistemas de gestión de innovación con enfoque en resultados económicos</t>
+        </is>
+      </c>
     </row>
-    <row r="9" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="64">
         <v>8</v>
       </c>
@@ -3229,8 +3337,26 @@
       <c r="AB9" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC9" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigadora y Profesora Titular, Universidad de La Sabana</t>
+        </is>
+      </c>
+      <c r="AD9" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingeniera de Alimentos
+Doctorado en Ciencia y Tecnología de Alimentos, Universidad Politécnica de Valencia</t>
+        </is>
+      </c>
+      <c r="AE9" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Más de 20 años de experiencia en docencia, investigación y gestión académica en educación superior
+Directora General de Investigación de la Universidad de La Sabana (2021–2025), liderando estrategias de investigación e innovación
+Investigadora Senior reconocida por Minciencias, líder de grupo y autora en ciencia de alimentos y nutrición</t>
+        </is>
+      </c>
     </row>
-    <row r="10" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="64">
         <v>9</v>
       </c>
@@ -3311,8 +3437,29 @@
       <c r="AB10" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC10" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor, investigador y experto en políticas educativas</t>
+        </is>
+      </c>
+      <c r="AD10" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licenciado en Filosofía (Universidad Javeriana)
+Magíster en Economía (Universidad de los Andes)</t>
+        </is>
+      </c>
+      <c r="AE10" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Más de 25 años de experiencia en educación
+Secretario de Educación de Bogotá (2005-2007)
+Exrector de la Universidad Distrital y Universidad CAFAM
+Consultor de UNESCO y Naciones Unidas en América Latina y África
+Miembro permanente de la Academia Colombiana de Pedagogía y Educación
+Actualmente funge como asesor del Ministerio de Educación</t>
+        </is>
+      </c>
     </row>
-    <row r="11" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11" s="64">
         <v>10</v>
       </c>
@@ -3393,8 +3540,28 @@
       <c r="AB11" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC11" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vicerrector de Medios y Mediaciones Pedagógicas, UNAD</t>
+        </is>
+      </c>
+      <c r="AD11" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingeniero Electrónico
+Doctor en Salud Pública
+Máster en Ingeniería Telemática
+Especialista en Gestión de la Innovación Tecnológica</t>
+        </is>
+      </c>
+      <c r="AE11" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Más de 20 años de experiencia en investigación, innovación, transformación digital y educación superior
+Vicerrector de Medios y Mediaciones Pedagógicas de la UNAD desde 2015, impulsando ecosistemas de aprendizaje digital e innovación educativa
+Líder en transformación digital, innovación educativa e inteligencia artificial aplicada a la educación</t>
+        </is>
+      </c>
     </row>
-    <row r="12" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="64">
         <v>11</v>
       </c>
@@ -3475,8 +3642,26 @@
       <c r="AB12" s="66" t="b">
         <v>1</v>
       </c>
+      <c r="AC12" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vicerrector de Servicios a Aspirantes, Estudiantes y Egresados, UNAD</t>
+        </is>
+      </c>
+      <c r="AD12" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Doctor en Educación a Distancia y Tecnología Instruccional</t>
+        </is>
+      </c>
+      <c r="AE12" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Representante del Comité Asesor ante el Consejo Nacional de Rectores del SUE
+Líder con amplia trayectoria en gestión y dirección universitaria en la UNAD
+Experiencia en cargos directivos como Vicerrector, Decano y Director de Planeación
+Autor de publicaciones sobre educación a distancia, calidad educativa y efectividad organizacional</t>
+        </is>
+      </c>
     </row>
-    <row r="13" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13" s="64">
         <v>12</v>
       </c>
@@ -3486,8 +3671,10 @@
       <c r="C13" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="D13" s="67" t="s">
-        <v>15</v>
+      <c r="D13" s="67" t="inlineStr">
+        <is>
+          <t>Ana Lucía Chávez Correal</t>
+        </is>
       </c>
       <c r="E13" s="67" t="s">
         <v>168</v>
@@ -3520,11 +3707,15 @@
       <c r="O13" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="P13" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q13" s="69" t="s">
-        <v>15</v>
+      <c r="P13" s="69" t="inlineStr">
+        <is>
+          <t>ana-lucia-chavez-correal</t>
+        </is>
+      </c>
+      <c r="Q13" s="69" t="inlineStr">
+        <is>
+          <t>Ana Lucía Chávez Correal</t>
+        </is>
       </c>
       <c r="R13" s="69" t="s">
         <v>143</v>
@@ -3556,6 +3747,26 @@
       </c>
       <c r="AB13" s="66" t="b">
         <v>1</v>
+      </c>
+      <c r="AC13" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrante del equipo académico del Programa Retos – ASCUN</t>
+        </is>
+      </c>
+      <c r="AD13" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Psicóloga, Universidad Católica de Colombia
+Magíster en Dirección Universitaria, Universidad de los Andes
+Especialista en Docencia Universitaria</t>
+        </is>
+      </c>
+      <c r="AE13" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrante del equipo académico-técnico de ASCUN y coordinadora académica del Programa Retos
+Amplia experiencia en dirección, planeación y gestión académica en educación superior
+Liderazgo en desarrollo curricular, calidad institucional y procesos de acreditación
+Participación en iniciativas nacionales de política educativa, incluyendo la Comisión Gestora del Plan Nacional Decenal de Educación 2016–2026</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/portal-web/data/source-conferencistas/Participacion jornadas.xlsx
+++ b/portal-web/data/source-conferencistas/Participacion jornadas.xlsx
@@ -2624,8 +2624,10 @@
       <c r="D2" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="67" t="s">
-        <v>161</v>
+      <c r="E2" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 de marzo - Soacha</t>
+        </is>
       </c>
       <c r="F2" s="67">
         <v>3</v>
@@ -2633,8 +2635,10 @@
       <c r="G2" s="67">
         <v>4</v>
       </c>
-      <c r="H2" s="67" t="s">
-        <v>98</v>
+      <c r="H2" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soacha</t>
+        </is>
       </c>
       <c r="I2" s="67"/>
       <c r="J2" s="67">
@@ -2661,14 +2665,18 @@
       <c r="S2" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="T2" s="69" t="s">
-        <v>98</v>
+      <c r="T2" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soacha</t>
+        </is>
       </c>
       <c r="U2" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="V2" s="69" t="s">
-        <v>100</v>
+      <c r="V2" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jornada de apertura realizada en Soacha con la participación del Grupo Estratégico.</t>
+        </is>
       </c>
       <c r="W2" s="69"/>
       <c r="X2" s="69"/>
@@ -2978,8 +2986,10 @@
       <c r="D6" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="67" t="s">
-        <v>165</v>
+      <c r="E6" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 de mayo - Chía</t>
+        </is>
       </c>
       <c r="F6" s="67">
         <v>5</v>
@@ -3081,8 +3091,10 @@
       <c r="D7" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="E7" s="67" t="s">
-        <v>165</v>
+      <c r="E7" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 de mayo - Chía</t>
+        </is>
       </c>
       <c r="F7" s="67">
         <v>5</v>
@@ -3491,8 +3503,10 @@
       <c r="K11" s="67">
         <v>515</v>
       </c>
-      <c r="L11" s="67" t="s">
-        <v>81</v>
+      <c r="L11" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conversatorio con vicerrectores de la UNAD y conferencia de la Dra. Ana Lucía Chávez Correal.</t>
+        </is>
       </c>
       <c r="M11" s="67" t="s">
         <v>46</v>
@@ -3593,8 +3607,10 @@
       <c r="K12" s="67">
         <v>515</v>
       </c>
-      <c r="L12" s="67" t="s">
-        <v>81</v>
+      <c r="L12" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conversatorio con vicerrectores de la UNAD y conferencia de la Dra. Ana Lucía Chávez Correal.</t>
+        </is>
       </c>
       <c r="M12" s="67" t="s">
         <v>46</v>
@@ -3695,8 +3711,10 @@
       <c r="K13" s="67">
         <v>515</v>
       </c>
-      <c r="L13" s="67" t="s">
-        <v>81</v>
+      <c r="L13" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conversatorio con vicerrectores de la UNAD y conferencia de la Dra. Ana Lucía Chávez Correal.</t>
+        </is>
       </c>
       <c r="M13" s="67" t="s">
         <v>46</v>
@@ -3736,8 +3754,10 @@
         <v>46</v>
       </c>
       <c r="X13" s="69"/>
-      <c r="Y13" s="69" t="s">
-        <v>151</v>
+      <c r="Y13" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fotografía de Ana Lucía Chávez Correal</t>
+        </is>
       </c>
       <c r="Z13" s="66">
         <v>12</v>

--- a/portal-web/data/source-conferencistas/Participacion jornadas.xlsx
+++ b/portal-web/data/source-conferencistas/Participacion jornadas.xlsx
@@ -3030,8 +3030,10 @@
       <c r="R6" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="S6" s="69" t="s">
-        <v>122</v>
+      <c r="S6" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 de mayo</t>
+        </is>
       </c>
       <c r="T6" s="69" t="s">
         <v>98</v>

--- a/portal-web/data/source-conferencistas/Participacion jornadas.xlsx
+++ b/portal-web/data/source-conferencistas/Participacion jornadas.xlsx
@@ -3165,9 +3165,25 @@
       <c r="AB7" s="66" t="b">
         <v>1</v>
       </c>
-      <c r="AC7" s="69"/>
-      <c r="AD7" s="69"/>
-      <c r="AE7" s="69"/>
+      <c r="AC7" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asesora de Aseguramiento de la Calidad de la Educación Superior, Universidad de Cundinamarca</t>
+        </is>
+      </c>
+      <c r="AD7" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licenciada en Biología y Química
+Magíster en Educación de Adultos
+Doctora en Educación</t>
+        </is>
+      </c>
+      <c r="AE7" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Más de 20 años de experiencia en cargos académicos y administrativos en distintas universidades colombianas
+Participación en procesos de calidad y mejora continua en instituciones de educación superior
+Par académica y asesora, fortaleciendo políticas y procesos educativos en universidades del país</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:31" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="64">
@@ -3280,8 +3296,10 @@
       <c r="C9" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="67" t="s">
-        <v>10</v>
+      <c r="D9" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luz Indira Sotelo Díaz</t>
+        </is>
       </c>
       <c r="E9" s="67" t="s">
         <v>166</v>
@@ -3317,8 +3335,10 @@
       <c r="P9" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="Q9" s="69" t="s">
-        <v>10</v>
+      <c r="Q9" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luz Indira Sotelo Díaz</t>
+        </is>
       </c>
       <c r="R9" s="69" t="s">
         <v>132</v>
@@ -3339,8 +3359,10 @@
         <v>41</v>
       </c>
       <c r="X9" s="69"/>
-      <c r="Y9" s="69" t="s">
-        <v>137</v>
+      <c r="Y9" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fotografía de Luz Indira Sotelo Díaz</t>
+        </is>
       </c>
       <c r="Z9" s="66">
         <v>8</v>
@@ -3483,8 +3505,10 @@
       <c r="C11" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="D11" s="67" t="s">
-        <v>13</v>
+      <c r="D11" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leonardo Emilio Yunda Perlaza</t>
+        </is>
       </c>
       <c r="E11" s="67" t="s">
         <v>168</v>
@@ -3522,8 +3546,10 @@
       <c r="P11" s="69" t="s">
         <v>142</v>
       </c>
-      <c r="Q11" s="69" t="s">
-        <v>13</v>
+      <c r="Q11" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leonardo Emilio Yunda Perlaza</t>
+        </is>
       </c>
       <c r="R11" s="69" t="s">
         <v>143</v>
@@ -3544,8 +3570,10 @@
         <v>46</v>
       </c>
       <c r="X11" s="69"/>
-      <c r="Y11" s="69" t="s">
-        <v>146</v>
+      <c r="Y11" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fotografía de Leonardo Emilio Yunda Perlaza</t>
+        </is>
       </c>
       <c r="Z11" s="66">
         <v>10</v>
